--- a/docs/Internship_artifacts/Unit_Test_Plan_v0.1.xlsx
+++ b/docs/Internship_artifacts/Unit_Test_Plan_v0.1.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
   <si>
     <t xml:space="preserve">Sl: No:</t>
   </si>
@@ -172,6 +172,54 @@
   </si>
   <si>
     <t xml:space="preserve">Valid MD file</t>
+  </si>
+  <si>
+    <t xml:space="preserve">add auto scroll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">auto scolll to lates chat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">auto scroll to latest answer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">auto scorlling successfully</t>
+  </si>
+  <si>
+    <t xml:space="preserve">add cloud databse </t>
+  </si>
+  <si>
+    <t xml:space="preserve">upload file and store embeddings into cloud data base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data stored on cloude data base or not</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data storde and fetch from cloud databsae succesfully</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui test and links check</t>
+  </si>
+  <si>
+    <t xml:space="preserve">click on buttons, slidbars, menus and links</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UI componets are working as expeted or not</t>
+  </si>
+  <si>
+    <t xml:space="preserve">working correctly</t>
+  </si>
+  <si>
+    <t>deployment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">after deployment goto url and check the working of website</t>
+  </si>
+  <si>
+    <t xml:space="preserve">website working as UX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">work as desined and expeted and as run on local system</t>
   </si>
 </sst>
 </file>
@@ -803,7 +851,7 @@
     <col bestFit="1" customWidth="1" min="2" max="2" style="1" width="30.421875"/>
     <col customWidth="1" min="3" max="3" style="1" width="55.5546875"/>
     <col bestFit="1" customWidth="1" min="4" max="4" style="1" width="40.94140625"/>
-    <col bestFit="1" customWidth="1" min="5" max="5" style="1" width="46.08203125"/>
+    <col bestFit="1" customWidth="1" min="5" max="5" style="1" width="47.22265625"/>
     <col customWidth="1" min="6" max="6" style="1" width="15.88671875"/>
     <col min="7" max="16384" style="1" width="9.140625"/>
   </cols>
@@ -1069,36 +1117,84 @@
       </c>
     </row>
     <row r="14" ht="14.25">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
+      <c r="A14" s="3">
+        <v>13</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="15" ht="14.25">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
+      <c r="A15" s="3">
+        <v>14</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="16" ht="14.25">
-      <c r="A16" s="9"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
+      <c r="A16" s="3">
+        <v>15</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="17" ht="14.25">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
+      <c r="A17" s="3">
+        <v>16</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="18" ht="14.25">
       <c r="A18" s="9"/>

--- a/docs/Internship_artifacts/Unit_Test_Plan_v0.1.xlsx
+++ b/docs/Internship_artifacts/Unit_Test_Plan_v0.1.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
   <si>
     <t xml:space="preserve">Sl: No:</t>
   </si>
@@ -220,6 +220,18 @@
   </si>
   <si>
     <t xml:space="preserve">work as desined and expeted and as run on local system</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> hashing of the file</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aupload same file again and observe the behaviour of the application</t>
+  </si>
+  <si>
+    <t xml:space="preserve">same file not upload</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shows a message and skipp same files</t>
   </si>
 </sst>
 </file>
@@ -849,7 +861,7 @@
   <cols>
     <col customWidth="1" min="1" max="1" style="1" width="7.77734375"/>
     <col bestFit="1" customWidth="1" min="2" max="2" style="1" width="30.421875"/>
-    <col customWidth="1" min="3" max="3" style="1" width="55.5546875"/>
+    <col bestFit="1" customWidth="1" min="3" max="3" style="1" width="57.8515625"/>
     <col bestFit="1" customWidth="1" min="4" max="4" style="1" width="40.94140625"/>
     <col bestFit="1" customWidth="1" min="5" max="5" style="1" width="47.22265625"/>
     <col customWidth="1" min="6" max="6" style="1" width="15.88671875"/>
@@ -1197,12 +1209,24 @@
       </c>
     </row>
     <row r="18" ht="14.25">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
+      <c r="A18" s="9">
+        <v>17</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="19" ht="14.25">
       <c r="A19" s="9"/>
@@ -1219,6 +1243,7 @@
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
       <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
     </row>
     <row r="21" ht="14.25">
       <c r="A21" s="9"/>
